--- a/artfynd/A 71571-2021 artfynd.xlsx
+++ b/artfynd/A 71571-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71571-2021 artfynd.xlsx
+++ b/artfynd/A 71571-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112213243</v>
+        <v>100582689</v>
       </c>
       <c r="B2" t="n">
-        <v>85439</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Landverktjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446893</v>
+        <v>446783</v>
       </c>
       <c r="R2" t="n">
-        <v>7033446</v>
+        <v>7033254</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112213244</v>
+        <v>112213243</v>
       </c>
       <c r="B3" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446838</v>
+        <v>446893</v>
       </c>
       <c r="R3" t="n">
-        <v>7033353</v>
+        <v>7033446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +867,398 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112213244</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ol-olssvarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>446837</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7033353</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112213246</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ol-olssvarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>446878</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7033465</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104163477</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Prostbölestigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>446823</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033283</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112213259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ol-olssvarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446861</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7033454</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71571-2021 artfynd.xlsx
+++ b/artfynd/A 71571-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100582689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213246</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104163477</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,8 +1289,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>